--- a/results/final_hsp90_evidence_matrix.xlsx
+++ b/results/final_hsp90_evidence_matrix.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>median rho=-0.246; 12/14 negative</t>
+          <t>median rho=-0.251; 11/12 negative</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>median rho=-0.246; mean rho=-0.221; 12/14 negative</t>
+          <t>median rho=-0.251; mean rho=-0.248; 11/12 negative</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>median rho=-0.246; 12/14 negative</t>
+          <t>median rho=-0.251; 11/12 negative</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>rho=0.322; N=43</t>
+          <t>rho=0.354; N=43</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.03527059433645797</v>
+        <v>0.01982647096370697</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.3131186506050664</v>
+        <v>0.3131186506050661</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>median rho=0.331; 14/14 positive</t>
+          <t>median rho=0.324; 12/12 positive</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -801,7 +801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -854,7 +854,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4-CHLOROPHENYLGUANIDINE</t>
+          <t>ALVESPIMYCIN</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -882,14 +882,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ALVESPIMYCIN</t>
+          <t>AT13387</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.2697628458498024</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.2131958061772029</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>AUC</t>
@@ -900,7 +904,11 @@
           <t>lower_is_more_sensitive</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>AT13387 (CTRP:688229)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -910,18 +918,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AT13387</t>
+          <t>BIIB021</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.2697628458498024</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.2131958061772029</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>AUC</t>
@@ -932,11 +936,7 @@
           <t>lower_is_more_sensitive</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>AT13387 (CTRP:688229)</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BIIB021</t>
+          <t>GANETESPIB</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -974,7 +974,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GANETESPIB</t>
+          <t>KW-2478</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GUANIDINE</t>
+          <t>NMS-E973</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KW-2478</t>
+          <t>PU-H71</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1058,14 +1058,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NMS-E973</t>
+          <t>SNX 2112</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.08483915403938094</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.5932083855972791</v>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>AUC</t>
@@ -1076,7 +1080,11 @@
           <t>lower_is_more_sensitive</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SNX 2112 (CTRP:362338)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1086,7 +1094,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PU-H71</t>
+          <t>SNX-5422</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1114,17 +1122,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SNX 2112</t>
+          <t>TANESPIMYCIN</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.08483915403938094</v>
+        <v>-0.1776735459662289</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5932083855972791</v>
+        <v>0.2727162570128552</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1138,7 +1146,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>SNX 2112 (CTRP:362338)</t>
+          <t>TANESPIMYCIN (CTRP:50134)</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1158,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SNX-5422</t>
+          <t>VER-49009</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1178,18 +1186,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TANESPIMYCIN</t>
+          <t>XL888</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>40</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.1776735459662289</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.2727162570128552</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>AUC</t>
@@ -1200,21 +1204,17 @@
           <t>lower_is_more_sensitive</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>TANESPIMYCIN (CTRP:50134)</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CTD2</t>
+          <t>CTRPv2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VER-49009</t>
+          <t>ALVESPIMYCIN</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1224,43 +1224,43 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AUC</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>lower_is_more_sensitive</t>
-        </is>
-      </c>
+          <t>CTRPv2_response</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CTD2</t>
+          <t>CTRPv2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>XL888</t>
+          <t>AT13387</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.2569169960474308</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.2366456770181237</v>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AUC</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>lower_is_more_sensitive</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>CTRPv2_response</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>AT13387 (CTRP:688229)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4-CHLOROPHENYLGUANIDINE</t>
+          <t>BIIB021</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ALVESPIMYCIN</t>
+          <t>GANETESPIB</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1318,29 +1318,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AT13387</t>
+          <t>KW-2478</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.2569169960474308</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.2366456770181237</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>CTRPv2_response</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>AT13387 (CTRP:688229)</t>
-        </is>
-      </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1350,7 +1342,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BIIB021</t>
+          <t>NMS-E973</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1374,7 +1366,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GANETESPIB</t>
+          <t>PU-H71</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1398,7 +1390,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GUANIDINE</t>
+          <t>SNX 2112</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1422,7 +1414,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KW-2478</t>
+          <t>SNX-5422</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1446,21 +1438,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NMS-E973</t>
+          <t>TANESPIMYCIN</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.2061446343130039</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.1902730206138747</v>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>CTRPv2_response</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>TANESPIMYCIN (CTRP:50134)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PU-H71</t>
+          <t>VER-49009</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SNX 2112</t>
+          <t>XL888</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1513,12 +1513,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CTRPv2</t>
+          <t>GDSC1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SNX-5422</t>
+          <t>ALVESPIMYCIN</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1528,53 +1528,53 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CTRPv2_response</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>AUC</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>lower_is_more_sensitive</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CTRPv2</t>
+          <t>GDSC1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TANESPIMYCIN</t>
+          <t>AT13387</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>42</v>
-      </c>
-      <c r="D27" t="n">
-        <v>-0.2061446343130039</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.1902730206138747</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CTRPv2_response</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>TANESPIMYCIN (CTRP:50134)</t>
-        </is>
-      </c>
+          <t>AUC</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>lower_is_more_sensitive</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CTRPv2</t>
+          <t>GDSC1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>VER-49009</t>
+          <t>BIIB021</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1584,21 +1584,25 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CTRPv2_response</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>AUC</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>lower_is_more_sensitive</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CTRPv2</t>
+          <t>GDSC1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>XL888</t>
+          <t>GANETESPIB</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1608,10 +1612,14 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CTRPv2_response</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>AUC</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>lower_is_more_sensitive</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -1622,7 +1630,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>4-CHLOROPHENYLGUANIDINE</t>
+          <t>KW-2478</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1650,7 +1658,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ALVESPIMYCIN</t>
+          <t>NMS-E973</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1678,7 +1686,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AT13387</t>
+          <t>PU-H71</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1706,7 +1714,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BIIB021</t>
+          <t>SNX 2112</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1734,7 +1742,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GANETESPIB</t>
+          <t>SNX-5422</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1762,14 +1770,18 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GUANIDINE</t>
+          <t>TANESPIMYCIN</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-0.4673913043478261</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.02452794323519294</v>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>AUC</t>
@@ -1780,7 +1792,11 @@
           <t>lower_is_more_sensitive</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Tanespimycin</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1790,7 +1806,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>KW-2478</t>
+          <t>VER-49009</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1818,7 +1834,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NMS-E973</t>
+          <t>XL888</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1841,12 +1857,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GDSC1</t>
+          <t>GDSC2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PU-H71</t>
+          <t>ALVESPIMYCIN</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1869,12 +1885,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GDSC1</t>
+          <t>GDSC2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SNX 2112</t>
+          <t>AT13387</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1897,12 +1913,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GDSC1</t>
+          <t>GDSC2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SNX-5422</t>
+          <t>BIIB021</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1925,23 +1941,19 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GDSC1</t>
+          <t>GDSC2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TANESPIMYCIN</t>
+          <t>GANETESPIB</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>23</v>
-      </c>
-      <c r="D41" t="n">
-        <v>-0.4673913043478261</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0.02452794323519294</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>AUC</t>
@@ -1952,21 +1964,17 @@
           <t>lower_is_more_sensitive</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Tanespimycin</t>
-        </is>
-      </c>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GDSC1</t>
+          <t>GDSC2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>VER-49009</t>
+          <t>KW-2478</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1989,12 +1997,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GDSC1</t>
+          <t>GDSC2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>XL888</t>
+          <t>NMS-E973</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -2022,7 +2030,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>4-CHLOROPHENYLGUANIDINE</t>
+          <t>PU-H71</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -2050,7 +2058,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ALVESPIMYCIN</t>
+          <t>SNX 2112</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -2078,7 +2086,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AT13387</t>
+          <t>SNX-5422</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -2106,14 +2114,18 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BIIB021</t>
+          <t>TANESPIMYCIN</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="D47" t="n">
+        <v>-0.2430830039525692</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.263720491259165</v>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
           <t>AUC</t>
@@ -2124,7 +2136,11 @@
           <t>lower_is_more_sensitive</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Tanespimycin</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2134,7 +2150,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GANETESPIB</t>
+          <t>VER-49009</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -2162,7 +2178,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GUANIDINE</t>
+          <t>XL888</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -2181,238 +2197,6 @@
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>GDSC2</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>KW-2478</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>AUC</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>lower_is_more_sensitive</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>GDSC2</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>NMS-E973</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>AUC</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>lower_is_more_sensitive</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>GDSC2</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>PU-H71</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>AUC</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>lower_is_more_sensitive</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>GDSC2</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>SNX 2112</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>AUC</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>lower_is_more_sensitive</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>GDSC2</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>SNX-5422</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>AUC</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>lower_is_more_sensitive</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>GDSC2</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>TANESPIMYCIN</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>23</v>
-      </c>
-      <c r="D55" t="n">
-        <v>-0.2430830039525692</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0.263720491259165</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>AUC</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>lower_is_more_sensitive</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Tanespimycin</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>GDSC2</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>VER-49009</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>AUC</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>lower_is_more_sensitive</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>GDSC2</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>XL888</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>AUC</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>lower_is_more_sensitive</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2497,25 +2281,25 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2213031422388208</v>
+        <v>-0.2475937877205824</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2460149560668337</v>
+        <v>-0.2509022911796019</v>
       </c>
       <c r="F2" t="n">
         <v>-0.6055572334642102</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1279814513014585</v>
+        <v>0.07274749721913237</v>
       </c>
       <c r="H2" t="n">
         <v>1407</v>
@@ -2530,10 +2314,10 @@
         <v>9.999000099990002e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.007011331103478403</v>
+        <v>-0.007079866982158381</v>
       </c>
       <c r="M2" t="n">
-        <v>0.054353365848878</v>
+        <v>0.05809556656976902</v>
       </c>
     </row>
   </sheetData>
@@ -2594,22 +2378,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2460149560668337</v>
+        <v>-0.2509022911796019</v>
       </c>
       <c r="E2" t="n">
         <v>9.999000099990002e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -2629,7 +2413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2662,267 +2446,229 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4-CHLOROPHENYLGUANIDINE</t>
+          <t>ALVESPIMYCIN</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>0.308174440338348</v>
+        <v>0.2435441326754003</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04437672162799396</v>
+        <v>0.1946671764001388</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ALVESPIMYCIN</t>
+          <t>AT13387</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
         <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2483034835700878</v>
+        <v>0.3165739710789767</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1858163574155127</v>
+        <v>0.08830235070547865</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AT13387</t>
+          <t>BIIB021</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C4" t="n">
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3286238756568276</v>
+        <v>0.2780499284383684</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07621517681278428</v>
+        <v>0.136817593336162</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BIIB021</t>
+          <t>GANETESPIB</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C5" t="n">
         <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3239514982778205</v>
+        <v>0.3146067435198066</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0807406130555955</v>
+        <v>0.09040699465200225</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GANETESPIB</t>
+          <t>KW-2478</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3470908910119507</v>
+        <v>0.3314704412545417</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0602153465452436</v>
+        <v>0.0299049443041285</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GUANIDINE</t>
+          <t>NMS-E973</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C7" t="n">
         <v>43</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3471530019960815</v>
+        <v>0.3470150724537035</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02256023208834077</v>
+        <v>0.02261754533515664</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KW-2478</t>
+          <t>PU-H71</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
         <v>43</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3167830867971992</v>
+        <v>0.3491919689427628</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03847916821274478</v>
+        <v>0.02172706541133545</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NMS-E973</t>
+          <t>SNX 2112</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
         <v>43</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3337235266970436</v>
+        <v>0.3482857614109044</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02874169551514223</v>
+        <v>0.02209412254134318</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PU-H71</t>
+          <t>SNX-5422</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
         <v>43</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3613502533285294</v>
+        <v>0.3584321517872078</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01727625223105556</v>
+        <v>0.01826730286316317</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SNX 2112</t>
+          <t>TANESPIMYCIN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3568192156692376</v>
+        <v>0.3079661847494773</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0188353583650404</v>
+        <v>0.09779374864678221</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SNX-5422</t>
+          <t>VER-49009</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
         <v>43</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3693214131525657</v>
+        <v>0.339840658550961</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01479753869811546</v>
+        <v>0.02577124734982442</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TANESPIMYCIN</t>
+          <t>XL888</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2874624558893847</v>
+        <v>0.3152210908426025</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1234842287577952</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>VER-49009</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>13</v>
-      </c>
-      <c r="C14" t="n">
-        <v>43</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.3355106685673316</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.02784590860131264</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>XL888</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>13</v>
-      </c>
-      <c r="C15" t="n">
-        <v>43</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.3207219489835454</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.03600332098697278</v>
+        <v>0.03949879529647581</v>
       </c>
     </row>
   </sheetData>
@@ -3084,7 +2830,7 @@
         <v>64</v>
       </c>
       <c r="C2" t="n">
-        <v>2.352564796379439</v>
+        <v>2.352564796379438</v>
       </c>
       <c r="D2" t="n">
         <v>0.1668741866827246</v>
@@ -3096,7 +2842,7 @@
         <v>0.5773537167338288</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.000430276820348352</v>
+        <v>-0.0004302768203487961</v>
       </c>
     </row>
     <row r="3">
@@ -3109,19 +2855,19 @@
         <v>64</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8754353000483069</v>
+        <v>0.8754353000483071</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3131186506050664</v>
+        <v>0.3131186506050661</v>
       </c>
       <c r="E3" t="n">
         <v>-0.0163982655367804</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7164746897883244</v>
+        <v>0.7164746897883242</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.007083710202404392</v>
+        <v>-0.00708371020240417</v>
       </c>
     </row>
     <row r="4">
@@ -3134,19 +2880,19 @@
         <v>64</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4521090163395226</v>
+        <v>0.4521090163395228</v>
       </c>
       <c r="D4" t="n">
-        <v>0.441945464340782</v>
+        <v>0.4419454643407813</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02372605811667997</v>
+        <v>0.02372605811667999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4396710640341321</v>
+        <v>0.4396710640341315</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.01752004017163755</v>
+        <v>-0.01752004017163777</v>
       </c>
     </row>
   </sheetData>
